--- a/database/seeders/data/04_CUENTAS_Y_MEMBRESIAS.xlsx
+++ b/database/seeders/data/04_CUENTAS_Y_MEMBRESIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\ParquesEsp\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F6088C-1916-4477-A858-502F0115E5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0175C1C-6BBF-46EF-90B1-2FFB8F23EC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="145">
   <si>
     <t>INSTRUCCIONES DE CAPTURA</t>
   </si>
@@ -161,6 +161,9 @@
     <t>PARQUE ESPAÑA</t>
   </si>
   <si>
+    <t>Individual</t>
+  </si>
+  <si>
     <t>Registro de ejemplo para el socio 1001.</t>
   </si>
   <si>
@@ -171,6 +174,9 @@
   </si>
   <si>
     <t>M-1003</t>
+  </si>
+  <si>
+    <t>Famliar</t>
   </si>
   <si>
     <t>Registro de ejemplo para el socio 1003.</t>
@@ -434,16 +440,22 @@
     <t>NOMBRE DEL ARCHIVO DE SOPORTE</t>
   </si>
   <si>
-    <t>EJEMPLOS: MEMBRESÍAS (UNA CUENTA EN DOS PARQUES)</t>
+    <t>EJEMPLOS: MEMBRESÍAS (UN PARQUE, DOS PARQUES, INDIVIDUAL Y FAMILIAR)</t>
   </si>
   <si>
     <t>PARQUE ESPAÑA I</t>
   </si>
   <si>
-    <t>FAMILIAR</t>
+    <t>INDIVIDUAL</t>
   </si>
   <si>
     <t>ACTIVA</t>
+  </si>
+  <si>
+    <t>INDIVIDUAL BÁSICA</t>
+  </si>
+  <si>
+    <t>FAMILIAR</t>
   </si>
   <si>
     <t>FAMILIAR ESTÁNDAR</t>
@@ -455,16 +467,10 @@
     <t>NO</t>
   </si>
   <si>
-    <t>INDIVIDUAL</t>
+    <t>INDIVIDUAL PLUS</t>
   </si>
   <si>
-    <t>INDIVIDUAL BÁSICA</t>
-  </si>
-  <si>
-    <t>Individual</t>
-  </si>
-  <si>
-    <t>Famliar</t>
+    <t>M-1004</t>
   </si>
 </sst>
 </file>
@@ -475,7 +481,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -524,8 +530,13 @@
       <color rgb="FF1E8449"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -572,6 +583,16 @@
         <fgColor rgb="FF2980B9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -615,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -649,7 +670,28 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -658,6 +700,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -883,11 +934,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -895,11 +946,11 @@
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -952,11 +1003,11 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
     </row>
     <row r="11" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
@@ -1017,22 +1068,22 @@
         <v>28</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -2862,52 +2913,52 @@
         <v>28</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K1" s="11" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -6719,28 +6770,28 @@
         <v>32</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -8942,17 +8993,17 @@
   <sheetPr>
     <tabColor rgb="FF1A252F"/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="17" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -8989,21 +9040,21 @@
     <row r="6" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
@@ -9057,7 +9108,7 @@
         <v>40</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>23</v>
@@ -9069,7 +9120,7 @@
         <v>39</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10" s="9">
         <v>46037</v>
@@ -9078,7 +9129,7 @@
         <v>22</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>22</v>
@@ -9089,7 +9140,7 @@
     </row>
     <row r="11" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>24</v>
@@ -9098,7 +9149,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>25</v>
@@ -9107,10 +9158,10 @@
         <v>24</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I11" s="9">
         <v>46044.291666666664</v>
@@ -9119,7 +9170,7 @@
         <v>24</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>24</v>
@@ -9130,7 +9181,7 @@
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>26</v>
@@ -9139,7 +9190,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>23</v>
@@ -9148,10 +9199,10 @@
         <v>26</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I12" s="9">
         <v>46051.333333333336</v>
@@ -9160,7 +9211,7 @@
         <v>26</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>26</v>
@@ -9171,49 +9222,49 @@
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
+      <c r="A15" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -9221,22 +9272,22 @@
         <v>39</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>22</v>
@@ -9250,25 +9301,25 @@
     </row>
     <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>24</v>
@@ -9282,25 +9333,25 @@
     </row>
     <row r="19" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>26</v>
@@ -9314,23 +9365,23 @@
     </row>
     <row r="21" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
+      <c r="A22" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
@@ -9340,1070 +9391,1163 @@
         <v>30</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L23" s="11" t="s">
         <v>21</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="10">
+      <c r="B24" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="14">
+        <v>1200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>1200</v>
+      </c>
+      <c r="H24" s="14">
+        <v>1200</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="19">
+        <v>46023</v>
+      </c>
+      <c r="K24" s="15"/>
+      <c r="L24" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="O24" s="13"/>
+    </row>
+    <row r="25" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="17">
         <v>2500</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G25" s="17">
         <v>2500</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H25" s="17">
         <v>2500</v>
       </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="13">
+      <c r="I25" s="17"/>
+      <c r="J25" s="20">
         <v>46023</v>
       </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="8" t="s">
+      <c r="K25" s="18"/>
+      <c r="L25" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="O25" s="16"/>
+    </row>
+    <row r="26" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="17">
+        <v>1800</v>
+      </c>
+      <c r="G26" s="17">
+        <v>1800</v>
+      </c>
+      <c r="H26" s="17">
+        <v>1800</v>
+      </c>
+      <c r="I26" s="17"/>
+      <c r="J26" s="20">
+        <v>46023</v>
+      </c>
+      <c r="K26" s="18"/>
+      <c r="L26" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="O26" s="16"/>
+    </row>
+    <row r="27" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1500</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1500</v>
+      </c>
+      <c r="H27" s="14">
+        <v>1500</v>
+      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="19">
+        <v>46054</v>
+      </c>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="O27" s="13"/>
+    </row>
+    <row r="28" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="M24" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="O24" s="8"/>
-    </row>
-    <row r="25" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="C28" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="14">
+        <v>2500</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2500</v>
+      </c>
+      <c r="H28" s="14">
+        <v>2500</v>
+      </c>
+      <c r="I28" s="13"/>
+      <c r="J28" s="19">
+        <v>46054</v>
+      </c>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="10">
-        <v>1800</v>
-      </c>
-      <c r="G25" s="10">
-        <v>1800</v>
-      </c>
-      <c r="H25" s="10">
-        <v>1800</v>
-      </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="13">
-        <v>46023</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="O25" s="8"/>
-    </row>
-    <row r="26" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="10">
-        <v>1200</v>
-      </c>
-      <c r="G26" s="10">
-        <v>1200</v>
-      </c>
-      <c r="H26" s="10">
-        <v>1200</v>
-      </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="13">
-        <v>46054</v>
-      </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="N26" s="8" t="s">
+      <c r="M28" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="N28" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="O26" s="8"/>
-    </row>
-    <row r="27" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="O28" s="13"/>
+    </row>
     <row r="29" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-    </row>
-    <row r="30" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+    </row>
+    <row r="30" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+    </row>
+    <row r="31" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="B31" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="C31" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="D31" s="12" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="8" t="s">
+      <c r="E31" s="12" t="s">
         <v>87</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E34" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-    </row>
-    <row r="37" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="12" t="s">
+      <c r="F34" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="23"/>
+      <c r="Q37" s="23"/>
+    </row>
+    <row r="38" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B38" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="11" t="s">
+      <c r="C38" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G37" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="J37" s="11" t="s">
+      <c r="E38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K37" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="M37" s="12" t="s">
+      <c r="K38" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="N37" s="12" t="s">
+      <c r="L38" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="O37" s="12" t="s">
+      <c r="M38" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="P37" s="12" t="s">
+      <c r="N38" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="Q37" s="12" t="s">
+      <c r="O38" s="12" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="9">
-        <v>46037</v>
-      </c>
-      <c r="H38" s="9">
-        <v>46037</v>
-      </c>
-      <c r="I38" s="8" t="s">
+      <c r="P38" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="J38" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M38" s="8" t="s">
+      <c r="Q38" s="12" t="s">
         <v>100</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="O38" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="P38" s="9">
-        <v>46037</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B39" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="9">
+        <v>46037</v>
+      </c>
+      <c r="H39" s="9">
+        <v>46037</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="N39" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39" s="9">
-        <v>46044.291666666664</v>
-      </c>
-      <c r="H39" s="9">
-        <v>46044.291666666664</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M39" s="8" t="s">
+      <c r="O39" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="N39" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="O39" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="P39" s="9">
-        <v>46044.291666666664</v>
+        <v>46037</v>
       </c>
       <c r="Q39" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="H40" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="P40" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="8" t="s">
+      <c r="B41" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="D41" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="9">
+      <c r="E41" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H41" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="I40" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="J40" s="8" t="s">
+      <c r="I41" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J41" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K40" s="8" t="s">
+      <c r="K41" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L40" s="8" t="s">
+      <c r="L41" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M40" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="P40" s="9">
+      <c r="M41" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="O41" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="P41" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="Q40" s="8" t="s">
+      <c r="Q41" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-    </row>
-    <row r="44" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="11" t="s">
+    <row r="42" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+    </row>
+    <row r="45" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B45" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D45" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E45" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="G44" s="12" t="s">
+      <c r="F45" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G45" s="12" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="9">
-        <v>46037</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46037</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="9">
-        <v>46044.291666666664</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="E46" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="9">
+      <c r="E47" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G47" s="8" t="s">
+      <c r="D48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-    </row>
-    <row r="51" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
+    <row r="49" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
+    </row>
+    <row r="52" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" s="11" t="s">
+      <c r="B52" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="D52" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G51" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="9">
-        <v>46037</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F52" s="10">
-        <v>2500</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>41</v>
+      <c r="E52" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="9">
+        <v>46037</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="10">
+        <v>2500</v>
+      </c>
+      <c r="G53" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B53" s="9">
-        <v>46044.291666666664</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F53" s="10">
-        <v>850</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" s="10">
+        <v>850</v>
+      </c>
+      <c r="G54" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="9">
+    </row>
+    <row r="55" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54" s="8" t="s">
+      <c r="C55" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F55" s="10">
         <v>1200</v>
       </c>
-      <c r="G54" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="16"/>
-    </row>
-    <row r="58" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="11" t="s">
+      <c r="G55" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="23"/>
+      <c r="L58" s="23"/>
+      <c r="M58" s="23"/>
+      <c r="N58" s="23"/>
+      <c r="O58" s="23"/>
+      <c r="P58" s="23"/>
+      <c r="Q58" s="23"/>
+    </row>
+    <row r="59" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58" s="11" t="s">
+      <c r="B59" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F58" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H58" s="11" t="s">
+      <c r="D59" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="G59" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="H59" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="I59" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K59" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L58" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="N58" s="12" t="s">
+      <c r="L59" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="O58" s="12" t="s">
+      <c r="M59" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="P58" s="12" t="s">
+      <c r="N59" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="Q58" s="12" t="s">
+      <c r="O59" s="12" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I59" s="10">
-        <v>2500</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="9">
-        <v>46037</v>
-      </c>
-      <c r="M59" s="9">
-        <v>46037</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="O59" s="9">
-        <v>46037</v>
-      </c>
-      <c r="P59" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q59" s="8" t="s">
-        <v>41</v>
+      <c r="P59" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q59" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="10">
+        <v>2500</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="9">
+        <v>46037</v>
+      </c>
+      <c r="M60" s="9">
+        <v>46037</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="O60" s="9">
+        <v>46037</v>
+      </c>
+      <c r="P60" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q60" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I60" s="10">
-        <v>850</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K60" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L60" s="9">
-        <v>46044.291666666664</v>
-      </c>
-      <c r="M60" s="9">
-        <v>46044.291666666664</v>
-      </c>
-      <c r="N60" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="O60" s="9">
-        <v>46044.291666666664</v>
-      </c>
-      <c r="P60" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q60" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61" s="10">
+        <v>850</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="M61" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="O61" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="P61" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q61" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="8" t="s">
+    </row>
+    <row r="62" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="C62" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="D62" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F62" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G62" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H61" s="8" t="s">
+      <c r="H62" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="10">
+      <c r="I62" s="10">
         <v>1200</v>
       </c>
-      <c r="J61" s="8" t="s">
+      <c r="J62" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K61" s="8" t="s">
+      <c r="K62" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L61" s="9">
+      <c r="L62" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="M61" s="9">
+      <c r="M62" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="N61" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="O61" s="9">
+      <c r="N62" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="O62" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="P61" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q61" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-    </row>
-    <row r="65" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="11" t="s">
+      <c r="P62" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q62" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="23"/>
+      <c r="I65" s="23"/>
+    </row>
+    <row r="66" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B65" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D65" s="11" t="s">
+      <c r="B66" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="C66" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="D66" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G65" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="I65" s="12" t="s">
+      <c r="G66" s="11" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H66" s="9">
-        <v>46037</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>100</v>
+      <c r="H66" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="G67" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H67" s="9">
-        <v>46044.291666666664</v>
+        <v>46037</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D68" s="8" t="s">
+      <c r="G68" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H68" s="9">
+        <v>46044.291666666664</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="C69" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F68" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G68" s="8" t="s">
+      <c r="D69" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G69" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H68" s="9">
+      <c r="H69" s="9">
         <v>46051.333333333336</v>
       </c>
-      <c r="I68" s="8" t="s">
-        <v>106</v>
+      <c r="I69" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A37:Q37"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A58:Q58"/>
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A36:Q36"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A57:Q57"/>
-    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14304,31 +14448,31 @@
         <v>28</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -16755,43 +16899,43 @@
         <v>30</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L1" s="11" t="s">
         <v>21</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
@@ -20201,19 +20345,19 @@
         <v>28</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -21847,49 +21991,49 @@
         <v>28</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J1" s="11" t="s">
         <v>21</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -25712,7 +25856,7 @@
         <v>33</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G1" s="12" t="s">
         <v>37</v>

--- a/database/seeders/data/04_CUENTAS_Y_MEMBRESIAS.xlsx
+++ b/database/seeders/data/04_CUENTAS_Y_MEMBRESIAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\ParquesEsp\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA9E57E-E0FA-4032-AEE7-1648F38B073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47263331-C627-4779-B8BB-70E75AF3E2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="289">
   <si>
     <t>INSTRUCCIONES DE CAPTURA</t>
   </si>
@@ -494,9 +494,6 @@
     </r>
   </si>
   <si>
-    <t>Identificador del grupo en el sistema anterior. Se usa para relacionar varias cuentas del mismo grupo (ej. una familia con cuentas en distintos clubes).</t>
-  </si>
-  <si>
     <t>ACTIVO o INACTIVO.</t>
   </si>
   <si>
@@ -523,15 +520,9 @@
     </r>
   </si>
   <si>
-    <t>Identificador de la cuenta de membresía en el sistema anterior. Se usa para relacionar esta cuenta en las demás hojas y archivos.</t>
-  </si>
-  <si>
     <t>Número de cuenta interno usado por el club, si es distinto al número de membresía.</t>
   </si>
   <si>
-    <t>Ver catálogo CLUBES en 02_CLUBES_Y_CONFIGURACION.</t>
-  </si>
-  <si>
     <t>INDIVIDUAL o FAMILIAR.</t>
   </si>
   <si>
@@ -539,9 +530,6 @@
   </si>
   <si>
     <t>Ver hoja GRUPOS DE CUENTAS. Solo si esta cuenta pertenece a un grupo con cuentas en varios clubes.</t>
-  </si>
-  <si>
-    <t>Formato AAAA-MM-DD. Fecha a partir de la cual el sistema debe generar cargos mensuales para esta cuenta; evita generar cargos retroactivos de meses ya cubiertos en el sistema anterior.</t>
   </si>
   <si>
     <t>Parque España I</t>
@@ -579,30 +567,6 @@
     <t>Ver hoja SOCIOS en 03_SOCIOS.</t>
   </si>
   <si>
-    <t>Nombre del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido paterno del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido materno del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Ver catálogo PARENTESCOS en 01_CATALOGOS. Relación de este integrante con el titular de la cuenta.</t>
-  </si>
-  <si>
-    <t>SÍ/NO: si este integrante es el titular de la cuenta.</t>
-  </si>
-  <si>
-    <t>Código o tarjeta de acceso de este integrante en este club, si ya existe.</t>
-  </si>
-  <si>
-    <t>Formato AAAA-MM-DD. Fecha hasta la que el código de acceso es válido, si aplica.</t>
-  </si>
-  <si>
-    <t>Ej. ACTIVO, INACTIVO.</t>
-  </si>
-  <si>
     <t>Titular</t>
   </si>
   <si>
@@ -671,25 +635,10 @@
     <t>Parte de la cuota mensual que corresponde específicamente a esta membresía.</t>
   </si>
   <si>
-    <t>Ej. SINGLE (una sola membresía) o SPLIT (dividida entre clubes).</t>
-  </si>
-  <si>
     <t>Formato AAAA-MM-DD.</t>
   </si>
   <si>
     <t>Formato AAAA-MM-DD. Dejar vacío si sigue vigente.</t>
-  </si>
-  <si>
-    <t>SÍ/NO: si esta membresía genera cargos mensuales.</t>
-  </si>
-  <si>
-    <t>Ver catálogo REGLAS DE PRECIOS en 01_CATALOGOS, si esta membresía sigue una regla de precio específica.</t>
-  </si>
-  <si>
-    <t>Ver catálogo REGLAS DE PAQUETE ENTRE CLUBES en este archivo, solo si esta membresía proviene de un paquete entre clubes.</t>
-  </si>
-  <si>
-    <t>SINGLE</t>
   </si>
   <si>
     <t>Familiar</t>
@@ -721,21 +670,6 @@
     </r>
   </si>
   <si>
-    <t>Cuenta de membresía a la que pertenece este dato fiscal. Ver hoja CUENTAS.</t>
-  </si>
-  <si>
-    <t>Nombre o razón social para facturación.</t>
-  </si>
-  <si>
-    <t>RFC del socio o de la razón social.</t>
-  </si>
-  <si>
-    <t>Ej. G03 - Gastos en general.</t>
-  </si>
-  <si>
-    <t>Ej. 605 - Sueldos y salarios.</t>
-  </si>
-  <si>
     <t>Código postal del domicilio fiscal (puede ser distinto al domicilio particular).</t>
   </si>
   <si>
@@ -774,9 +708,6 @@
     </r>
   </si>
   <si>
-    <t>Ver hoja GRUPOS DE CUENTAS, solo si el permiso aplica a todo el grupo. Dejar vacío si aplica solo a la cuenta indicada.</t>
-  </si>
-  <si>
     <t>Porcentaje de la cuota mensual que se sigue cobrando durante la ausencia, ej. 25%.</t>
   </si>
   <si>
@@ -786,16 +717,10 @@
     <t>SÍ/NO.</t>
   </si>
   <si>
-    <t>Nombre/ruta del archivo de soporte del permiso (se sube aparte), si aplica.</t>
-  </si>
-  <si>
     <t>Notas adicionales sobre el permiso.</t>
   </si>
   <si>
     <t>Correo de la persona que autorizó el permiso.</t>
-  </si>
-  <si>
-    <t>Ver catálogo CONCEPTOS DE COBRO en 01_CATALOGOS, ej. CUOTA_PERMISO (25%) o CUOTA_75_PERMISO (75%).</t>
   </si>
   <si>
     <t>25%</t>
@@ -839,18 +764,6 @@
     <t>Cuenta de membresía cancelada. Ver hoja CUENTAS.</t>
   </si>
   <si>
-    <t>VOLUNTARIA (a solicitud del titular) o SANCIÓN (por sanción disciplinaria).</t>
-  </si>
-  <si>
-    <t>Ver catálogo MOTIVOS CANCELACION en 01_CATALOGOS.</t>
-  </si>
-  <si>
-    <t>Correo de la persona que registró la cancelación.</t>
-  </si>
-  <si>
-    <t>Nombre/ruta del archivo de la carta de cancelación (se sube aparte), si aplica.</t>
-  </si>
-  <si>
     <t>VOLUNTARIA</t>
   </si>
   <si>
@@ -880,24 +793,6 @@
     </r>
   </si>
   <si>
-    <t>Cuenta de membresía reactivada. Ver hoja CUENTAS.</t>
-  </si>
-  <si>
-    <t>Correo de la persona que registró la reactivación.</t>
-  </si>
-  <si>
-    <t>SÍ/NO: si se solicitó documentación nueva para reactivar.</t>
-  </si>
-  <si>
-    <t>SÍ/NO: si se cobró una cuota de inscripción al reactivar.</t>
-  </si>
-  <si>
-    <t>Importe cobrado por inscripción, en MXN, si aplica.</t>
-  </si>
-  <si>
-    <t>Notas adicionales sobre la reactivación.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -921,31 +816,13 @@
     <t>Club de la membresía que va a cambiar de tipo. Ver hoja MEMBRESIAS.</t>
   </si>
   <si>
-    <t>Ver catálogo TIPOS MEMBRESIA en 01_CATALOGOS.</t>
-  </si>
-  <si>
     <t>Ej. FAMILIAR_A_SOLIDARIA, SOLIDARIA_A_INDIVIDUAL.</t>
   </si>
   <si>
-    <t>Cuota mensual con el nuevo tipo de membresía, en MXN.</t>
-  </si>
-  <si>
     <t>PENDIENTE, PROMOVIDA o DESCARTADA.</t>
   </si>
   <si>
-    <t>Formato AAAA-MM-DD. Solo si el cambio ya se aplicó.</t>
-  </si>
-  <si>
     <t>Correo de la persona que aplicó el cambio.</t>
-  </si>
-  <si>
-    <t>Formato AAAA-MM-DD. Solo si la transición fue descartada.</t>
-  </si>
-  <si>
-    <t>Correo de la persona que descartó la transición.</t>
-  </si>
-  <si>
-    <t>Motivo por el que se descartó la transición.</t>
   </si>
   <si>
     <t>Solidaria</t>
@@ -974,27 +851,6 @@
     </r>
   </si>
   <si>
-    <t>Cuenta de membresía de la que se separa este integrante. Ver hoja CUENTAS.</t>
-  </si>
-  <si>
-    <t>Nombre del socio que se separa, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido paterno, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido materno, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Ver catálogo MOTIVOS SEPARACION en 01_CATALOGOS.</t>
-  </si>
-  <si>
-    <t>Número de la nueva cuenta de membresía creada para este socio. Ver hoja CUENTAS.</t>
-  </si>
-  <si>
-    <t>Nombre/ruta del archivo de soporte de la separación (se sube aparte), si aplica.</t>
-  </si>
-  <si>
     <t>Cambio de tipo por edad</t>
   </si>
   <si>
@@ -1048,24 +904,6 @@
     <t>VÁLIDA HASTA</t>
   </si>
   <si>
-    <t>Ver catálogo TIPOS MEMBRESIA en 01_CATALOGOS, si el paquete requiere un tipo de membresía específico en el club de origen.</t>
-  </si>
-  <si>
-    <t>Ver catálogo TIPOS MEMBRESIA en 01_CATALOGOS. Tipo de membresía que se otorga en el club destino.</t>
-  </si>
-  <si>
-    <t>Código interno del paquete entre clubes.</t>
-  </si>
-  <si>
-    <t>Años mínimos de antigüedad requeridos en el club de origen, si aplica.</t>
-  </si>
-  <si>
-    <t>SÍ/NO: si la membresía en el club de origen debe estar activa para aplicar el paquete.</t>
-  </si>
-  <si>
-    <t>Número de prioridad; menor número = mayor prioridad.</t>
-  </si>
-  <si>
     <t>Formato AAAA-MM-DD, si la regla tiene vigencia limitada.</t>
   </si>
   <si>
@@ -1091,6 +929,168 @@
   </si>
   <si>
     <t>PE2_INTERMEDIATE_PACKAGE</t>
+  </si>
+  <si>
+    <t>Ver CLUBES en 02_CLUBES_Y_CONFIGURACION.</t>
+  </si>
+  <si>
+    <t>Ver  TIPOS MEMBRESIA en 01_CATALOGOS, si el paquete requiere un tipo de membresía específico en el club de origen.</t>
+  </si>
+  <si>
+    <t>Ver  TIPOS MEMBRESIA en 01_CATALOGOS. Tipo de membresia que se otorga en el club destino</t>
+  </si>
+  <si>
+    <t>Años mínimos de antigüedad requeridos en el club de origen</t>
+  </si>
+  <si>
+    <t>SÍ/NO: si la membresía en el club de origen debe estar activa para aplicar el paquete</t>
+  </si>
+  <si>
+    <t>Número de prioridad</t>
+  </si>
+  <si>
+    <t>Identificador del grupo en el sistema anterior. Se usa para relacionar varias cuentas del mismo grupo (ej. una familia con cuentas en distintos clubes)</t>
+  </si>
+  <si>
+    <t>Num de membresía</t>
+  </si>
+  <si>
+    <t>Ver CLUBES en 02_CLUBES_Y_CONFIGURACION</t>
+  </si>
+  <si>
+    <t>Formato AAAA-MM-DD. Fecha a partir de la cual el sistema debe generar cargos mensuales para esta cuenta</t>
+  </si>
+  <si>
+    <t>Nombre del socio</t>
+  </si>
+  <si>
+    <t>Apellido paterno del socio</t>
+  </si>
+  <si>
+    <t>Apellido materno del soci</t>
+  </si>
+  <si>
+    <t>Ver PARENTESCOS en 01_CATALOGOS. Relación de este integrante con el titular de la cuenta</t>
+  </si>
+  <si>
+    <t>SÍ/NO</t>
+  </si>
+  <si>
+    <t>Código o tarjeta de acceso de este integrante en este club</t>
+  </si>
+  <si>
+    <t>Formato AAAA-MM-DD. Fecha hasta la que el código de acceso es válido</t>
+  </si>
+  <si>
+    <t>ACTIVO, INACTIVO</t>
+  </si>
+  <si>
+    <t>SINGULAR / DIVIDIDA</t>
+  </si>
+  <si>
+    <t>SINGULAR</t>
+  </si>
+  <si>
+    <t>Ver REGLAS DE PRECIOS en 01_CATALOGOS, si esta membresía sigue una regla de precio específica</t>
+  </si>
+  <si>
+    <t>Ver REGLAS DE PAQUETE ENTRE CLUBES en este archivo, solo si esta membresía proviene de un paquete entre clubes</t>
+  </si>
+  <si>
+    <t>Cuenta de membresía a la que pertenece este dato fiscal.</t>
+  </si>
+  <si>
+    <t>Nombre o razn social para facturacion</t>
+  </si>
+  <si>
+    <t>RFC del socio o de la razón social</t>
+  </si>
+  <si>
+    <t>Ej. 605</t>
+  </si>
+  <si>
+    <t>Ej. G03</t>
+  </si>
+  <si>
+    <t>Ver hoja GRUPOS DE CUENTAS, solo si el permiso aplica a todo el grup</t>
+  </si>
+  <si>
+    <t>Identificador de la cuenta de membresía</t>
+  </si>
+  <si>
+    <t>Nombre/ruta del archivo</t>
+  </si>
+  <si>
+    <t>Ver  CONCEPTOS DE COBRO en 01_CATALOGOS, ej. CUOTA_PERMISO (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOLUNTARIA o SANCIÓN </t>
+  </si>
+  <si>
+    <t>Ver  MOTIVOS CANCELACION en 01_CATALOGOS</t>
+  </si>
+  <si>
+    <t>Correo de la persona que registró la cancelación</t>
+  </si>
+  <si>
+    <t>SÍ/NO: si se solicitó documentación nueva para reactivar</t>
+  </si>
+  <si>
+    <t>Correo de la persona que registró la reactivación</t>
+  </si>
+  <si>
+    <t>SÍ/NO: si se cobró una cuota de inscripción al reactivar</t>
+  </si>
+  <si>
+    <t>Importe cobrado por inscripcion, en MXN</t>
+  </si>
+  <si>
+    <t>Notas adicionales sobre la reactivación</t>
+  </si>
+  <si>
+    <t>Formato AAAA-MM-DD</t>
+  </si>
+  <si>
+    <t>Cuenta de membresía reactivada. Ver hoja CUENTAS</t>
+  </si>
+  <si>
+    <t>Ver hoja 03_SOCIOS.</t>
+  </si>
+  <si>
+    <t>Ver catalogo TIPOS MEMBRESIA en 01_CATALOGOS</t>
+  </si>
+  <si>
+    <t>Cuota mensual con el nuevo tipo de membresía, en MXN</t>
+  </si>
+  <si>
+    <t>Formato AAAA-MM-DD. Solo si el cambio ya se aplico</t>
+  </si>
+  <si>
+    <t>Formato AAAA-MM-DD. Solo si la transición fue descartada</t>
+  </si>
+  <si>
+    <t>Correo de la persona que descartó la transición</t>
+  </si>
+  <si>
+    <t>Motivo por el que se descartó la transición</t>
+  </si>
+  <si>
+    <t>Cuenta de membresía de la que se separa este integrante. Ver hoja CUENTAS</t>
+  </si>
+  <si>
+    <t>Apellido paterno</t>
+  </si>
+  <si>
+    <t>Apellido materno</t>
+  </si>
+  <si>
+    <t>Ver MOTIVOS SEPARACION en 01_CATALOGOS</t>
+  </si>
+  <si>
+    <t>Número de la nueva cuenta de membresía creada para este socio. Ver hoja CUENTAS</t>
+  </si>
+  <si>
+    <t>Codigo interno del paquete entre clubes</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1101,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1173,6 +1173,27 @@
       <sz val="9"/>
       <color rgb="FFB0BEC5"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1304,7 +1325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1372,6 +1393,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1383,6 +1405,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1607,11 +1636,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1619,11 +1648,11 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1676,11 +1705,11 @@
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
@@ -1730,19 +1759,19 @@
     <col min="4" max="4" width="28.6328125" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="28.6328125" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="7" max="7" width="26.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -1768,26 +1797,26 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>240</v>
+      <c r="A3" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -1804,44 +1833,45 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="3" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="6" width="20.81640625" customWidth="1"/>
     <col min="7" max="7" width="31.1796875" customWidth="1"/>
     <col min="8" max="8" width="29.90625" customWidth="1"/>
-    <col min="9" max="9" width="23.36328125" customWidth="1"/>
+    <col min="9" max="9" width="31.1796875" customWidth="1"/>
     <col min="10" max="10" width="24.7265625" customWidth="1"/>
     <col min="11" max="11" width="42.90625" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="29.90625" customWidth="1"/>
-    <col min="14" max="14" width="19.453125" customWidth="1"/>
+    <col min="14" max="14" width="26.7265625" customWidth="1"/>
     <col min="15" max="15" width="42.90625" customWidth="1"/>
-    <col min="16" max="16" width="22.08984375" customWidth="1"/>
+    <col min="16" max="16" width="35.08984375" customWidth="1"/>
     <col min="17" max="17" width="31.1796875" customWidth="1"/>
-    <col min="18" max="18" width="24.7265625" customWidth="1"/>
+    <col min="18" max="18" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -1901,58 +1931,50 @@
     </row>
     <row r="3" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>243</v>
+        <v>157</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>277</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>214</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="K3" s="22"/>
       <c r="L3" s="22" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="N3" s="22" t="s">
-        <v>247</v>
+        <v>176</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>279</v>
       </c>
       <c r="O3" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="P3" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q3" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="R3" s="22" t="s">
-        <v>251</v>
+        <v>210</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q3" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="R3" s="33" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -1960,13 +1982,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
         <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -1975,13 +1997,13 @@
         <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="H4" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="I4" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="J4">
         <v>850</v>
@@ -2011,26 +2033,26 @@
   <cols>
     <col min="1" max="1" width="37.7265625" customWidth="1"/>
     <col min="2" max="2" width="19.453125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="5" width="20.81640625" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="3" max="3" width="36.6328125" customWidth="1"/>
+    <col min="4" max="4" width="20.81640625" customWidth="1"/>
+    <col min="5" max="6" width="36.90625" customWidth="1"/>
     <col min="7" max="7" width="36.36328125" customWidth="1"/>
     <col min="8" max="8" width="24.7265625" customWidth="1"/>
     <col min="9" max="9" width="37.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -2062,32 +2084,32 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>260</v>
+      <c r="A3" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>287</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>261</v>
+        <v>176</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -2098,7 +2120,7 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
         <v>69</v>
@@ -2107,7 +2129,7 @@
         <v>70</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="G4" t="s">
         <v>45</v>
@@ -2116,7 +2138,7 @@
         <v>46266</v>
       </c>
       <c r="I4" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2138,54 +2160,57 @@
     <col min="4" max="4" width="46.26953125" customWidth="1"/>
     <col min="5" max="5" width="44.90625" customWidth="1"/>
     <col min="6" max="7" width="45" customWidth="1"/>
-    <col min="8" max="11" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.1796875" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="C2" s="23" t="s">
         <v>73</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="K2" s="23" t="s">
         <v>23</v>
@@ -2193,54 +2218,54 @@
     </row>
     <row r="3" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>274</v>
+        <v>235</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>236</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>276</v>
+        <v>237</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>288</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G4" t="s">
         <v>62</v>
@@ -2254,19 +2279,19 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G5" t="s">
         <v>62</v>
@@ -2280,19 +2305,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G6" t="s">
         <v>62</v>
@@ -2306,19 +2331,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G7" t="s">
         <v>62</v>
@@ -2332,19 +2357,19 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E8" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G8" t="s">
         <v>62</v>
@@ -2358,19 +2383,19 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G9" t="s">
         <v>62</v>
@@ -2384,19 +2409,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G10" t="s">
         <v>62</v>
@@ -2410,19 +2435,19 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="E11" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G11" t="s">
         <v>62</v>
@@ -2436,19 +2461,19 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C12" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D12" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G12" t="s">
         <v>62</v>
@@ -2462,19 +2487,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D13" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="E13" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G13" t="s">
         <v>62</v>
@@ -2488,19 +2513,19 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D14" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="E14" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G14" t="s">
         <v>62</v>
@@ -2514,19 +2539,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="E15" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G15" t="s">
         <v>62</v>
@@ -2540,19 +2565,19 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G16" t="s">
         <v>62</v>
@@ -2566,19 +2591,19 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C17" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="E17" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
         <v>62</v>
@@ -2592,19 +2617,19 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E18" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G18" t="s">
         <v>62</v>
@@ -2618,19 +2643,19 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="E19" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G19" t="s">
         <v>62</v>
@@ -2644,19 +2669,19 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D20" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E20" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G20" t="s">
         <v>62</v>
@@ -2670,19 +2695,19 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E21" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G21" t="s">
         <v>62</v>
@@ -2696,19 +2721,19 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E22" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G22" t="s">
         <v>62</v>
@@ -2722,19 +2747,19 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="D23" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E23" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G23" t="s">
         <v>62</v>
@@ -2748,19 +2773,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G24" t="s">
         <v>62</v>
@@ -2774,19 +2799,19 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G25" t="s">
         <v>62</v>
@@ -2800,19 +2825,19 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="D26" t="s">
         <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G26" t="s">
         <v>62</v>
@@ -2826,19 +2851,19 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="D27" t="s">
         <v>41</v>
       </c>
       <c r="E27" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G27" t="s">
         <v>62</v>
@@ -2852,19 +2877,19 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D28" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="E28" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G28" t="s">
         <v>62</v>
@@ -2878,19 +2903,19 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="D29" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="E29" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G29" t="s">
         <v>62</v>
@@ -2904,19 +2929,19 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C30" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D30" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="E30" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G30" t="s">
         <v>62</v>
@@ -2930,19 +2955,19 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="D31" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="E31" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G31" t="s">
         <v>62</v>
@@ -2956,19 +2981,19 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C32" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="D32" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E32" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G32" t="s">
         <v>62</v>
@@ -2982,19 +3007,19 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="D33" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E33" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G33" t="s">
         <v>62</v>
@@ -3008,19 +3033,19 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="D34" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E34" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G34" t="s">
         <v>62</v>
@@ -3034,19 +3059,19 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G35" t="s">
         <v>62</v>
@@ -3078,10 +3103,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="30"/>
+      <c r="B1" s="31"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
@@ -3118,21 +3143,21 @@
     <row r="6" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
@@ -3300,18 +3325,18 @@
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
     </row>
     <row r="16" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
@@ -3443,23 +3468,23 @@
     </row>
     <row r="21" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
     </row>
     <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
@@ -3721,14 +3746,14 @@
       <c r="O29" s="18"/>
     </row>
     <row r="30" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
@@ -3811,25 +3836,25 @@
       </c>
     </row>
     <row r="37" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
     </row>
     <row r="38" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
@@ -4046,15 +4071,15 @@
     <row r="42" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="43" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="44" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
     </row>
     <row r="45" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
@@ -4150,15 +4175,15 @@
     </row>
     <row r="49" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="51" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
     </row>
     <row r="52" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
@@ -4253,25 +4278,25 @@
       </c>
     </row>
     <row r="58" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
     </row>
     <row r="59" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
@@ -4486,17 +4511,17 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="30"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="31"/>
+      <c r="I65" s="31"/>
     </row>
     <row r="66" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
@@ -4616,16 +4641,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A58:Q58"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A22:O22"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A37:Q37"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A58:Q58"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A15:J15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4636,15 +4661,15 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.453125" customWidth="1"/>
+    <col min="1" max="1" width="63.6328125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="32"/>
     </row>
     <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -4656,15 +4681,15 @@
     </row>
     <row r="3" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>146</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -4686,22 +4711,22 @@
     <col min="1" max="1" width="24.7265625" customWidth="1"/>
     <col min="2" max="2" width="31.1796875" customWidth="1"/>
     <col min="3" max="3" width="19.453125" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="4" max="4" width="29.6328125" customWidth="1"/>
+    <col min="5" max="5" width="22.1796875" customWidth="1"/>
     <col min="6" max="6" width="32.453125" customWidth="1"/>
     <col min="7" max="7" width="42.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -4727,26 +4752,26 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="F3" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>155</v>
-      </c>
       <c r="G3" s="22" t="s">
-        <v>156</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -4754,7 +4779,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
         <v>85</v>
@@ -4771,7 +4796,7 @@
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
         <v>88</v>
@@ -4780,7 +4805,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G5" s="24">
         <v>46023</v>
@@ -4791,13 +4816,13 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
         <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G6" s="24">
         <v>46054</v>
@@ -4816,29 +4841,29 @@
   <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
     <col min="2" max="2" width="19.453125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="20.81640625" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" customWidth="1"/>
+    <col min="8" max="8" width="26.54296875" customWidth="1"/>
     <col min="9" max="9" width="24.7265625" customWidth="1"/>
     <col min="10" max="10" width="22.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -4873,35 +4898,35 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
-        <v>161</v>
+      <c r="A3" s="33" t="s">
+        <v>242</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>164</v>
+        <v>246</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>165</v>
+        <v>247</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -4921,13 +4946,13 @@
         <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G4" t="s">
         <v>62</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
@@ -4950,13 +4975,13 @@
         <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G5" t="s">
         <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="J5" t="s">
         <v>23</v>
@@ -4970,7 +4995,7 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D6" t="s">
         <v>69</v>
@@ -4979,13 +5004,13 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="G6" t="s">
         <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="J6" t="s">
         <v>23</v>
@@ -5008,16 +5033,16 @@
         <v>66</v>
       </c>
       <c r="F7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G7" t="s">
         <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="J7" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -5043,31 +5068,31 @@
     <col min="8" max="8" width="35.90625" customWidth="1"/>
     <col min="9" max="9" width="30.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.453125" customWidth="1"/>
-    <col min="11" max="11" width="26.7265625" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="11" max="11" width="28.90625" customWidth="1"/>
+    <col min="12" max="12" width="24.26953125" customWidth="1"/>
     <col min="13" max="13" width="23.36328125" customWidth="1"/>
-    <col min="14" max="14" width="26.54296875" customWidth="1"/>
+    <col min="14" max="14" width="40.90625" customWidth="1"/>
     <col min="15" max="15" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -5118,49 +5143,49 @@
     </row>
     <row r="3" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="N3" s="22" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="O3" s="22" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -5168,7 +5193,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
@@ -5186,7 +5211,7 @@
         <v>1200</v>
       </c>
       <c r="I4" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="J4" s="24">
         <v>46023</v>
@@ -5203,10 +5228,10 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
         <v>62</v>
@@ -5220,8 +5245,8 @@
       <c r="H5">
         <v>2500</v>
       </c>
-      <c r="I5" t="s">
-        <v>194</v>
+      <c r="I5" s="25" t="s">
+        <v>254</v>
       </c>
       <c r="J5" s="24">
         <v>46023</v>
@@ -5238,10 +5263,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -5255,20 +5280,20 @@
       <c r="H6">
         <v>3650</v>
       </c>
-      <c r="I6" t="s">
-        <v>194</v>
+      <c r="I6" s="25" t="s">
+        <v>254</v>
       </c>
       <c r="J6" s="24">
         <v>46054</v>
       </c>
       <c r="L6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M6" t="s">
         <v>62</v>
       </c>
       <c r="O6" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -5284,22 +5309,22 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
+    <col min="1" max="1" width="29.90625" customWidth="1"/>
     <col min="2" max="2" width="27.26953125" customWidth="1"/>
     <col min="3" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="18.1796875" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="6" max="6" width="39.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -5323,22 +5348,22 @@
     </row>
     <row r="3" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>199</v>
+        <v>257</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -5346,19 +5371,19 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -5371,14 +5396,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.453125" customWidth="1"/>
+    <col min="1" max="1" width="36.1796875" customWidth="1"/>
     <col min="2" max="2" width="24.7265625" customWidth="1"/>
     <col min="3" max="3" width="19.453125" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" customWidth="1"/>
+    <col min="5" max="5" width="25.90625" customWidth="1"/>
+    <col min="6" max="6" width="20.81640625" customWidth="1"/>
     <col min="7" max="7" width="19.453125" customWidth="1"/>
     <col min="8" max="8" width="20.81640625" customWidth="1"/>
     <col min="9" max="9" width="24.7265625" customWidth="1"/>
@@ -5386,32 +5412,32 @@
     <col min="11" max="11" width="42.90625" customWidth="1"/>
     <col min="12" max="12" width="27.26953125" customWidth="1"/>
     <col min="13" max="13" width="23.36328125" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="14" max="14" width="29.6328125" customWidth="1"/>
     <col min="15" max="15" width="31.1796875" customWidth="1"/>
     <col min="16" max="16" width="27.26953125" customWidth="1"/>
-    <col min="17" max="17" width="22.08984375" customWidth="1"/>
+    <col min="17" max="17" width="35.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
     </row>
     <row r="2" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
@@ -5468,60 +5494,54 @@
     </row>
     <row r="3" spans="1:17" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>161</v>
+        <v>263</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>165</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>212</v>
-      </c>
       <c r="J3" s="22" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="N3" s="22" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="O3" s="22" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="P3" s="22" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="Q3" s="22" t="s">
-        <v>218</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
@@ -5545,10 +5565,10 @@
         <v>46265</v>
       </c>
       <c r="I4" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="J4" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="K4" t="s">
         <v>62</v>
@@ -5557,26 +5577,30 @@
         <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="N4" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="O4" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="P4" s="24">
         <v>46193</v>
       </c>
       <c r="Q4" t="s">
-        <v>224</v>
-      </c>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="L10" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="146" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5587,21 +5611,21 @@
   <cols>
     <col min="1" max="1" width="24.7265625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="24.7265625" customWidth="1"/>
+    <col min="3" max="3" width="38.6328125" customWidth="1"/>
     <col min="4" max="4" width="27.26953125" customWidth="1"/>
     <col min="5" max="5" width="29.90625" customWidth="1"/>
     <col min="6" max="6" width="44.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -5625,22 +5649,22 @@
     </row>
     <row r="3" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>230</v>
+        <v>176</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -5651,16 +5675,16 @@
         <v>46249</v>
       </c>
       <c r="C4" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
         <v>117</v>
       </c>
       <c r="F4" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
